--- a/student_results.xlsx
+++ b/student_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,6 +617,102 @@
         </is>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mayuri Hadap</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Btech</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>90</v>
+      </c>
+      <c r="E5" t="n">
+        <v>91</v>
+      </c>
+      <c r="F5" t="n">
+        <v>92</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93</v>
+      </c>
+      <c r="H5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I5" t="n">
+        <v>460</v>
+      </c>
+      <c r="J5" t="n">
+        <v>92</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rituja</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Btech</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>92</v>
+      </c>
+      <c r="E6" t="n">
+        <v>94</v>
+      </c>
+      <c r="F6" t="n">
+        <v>96</v>
+      </c>
+      <c r="G6" t="n">
+        <v>97</v>
+      </c>
+      <c r="H6" t="n">
+        <v>98</v>
+      </c>
+      <c r="I6" t="n">
+        <v>477</v>
+      </c>
+      <c r="J6" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
